--- a/Excel/音效表.xlsx
+++ b/Excel/音效表.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SoundEffect/4_ScoreLose_260812</t>
+          <t>SoundEffect/4_ScoreLose_260813_1|SoundEffect/4_ScoreLose_260813_2</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>对话逐字显示音（打字机，节奏靠最短间隔）</t>
+          <t>对话逐字显示音：单声击键采样池（由原连击音按波形拆分），一字一声随机挑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SoundEffect/8_TypingKeyboard_260812</t>
+          <t>SoundEffect/TypingTaps/*</t>
         </is>
       </c>
       <c r="D13" t="n">

--- a/Excel/音效表.xlsx
+++ b/Excel/音效表.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -750,6 +750,29 @@
         <v>0.055</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bgm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>背景音乐：全程循环主题曲（BgmManager 消费，非一次性音效通道）</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SoundEffect/BGM</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
